--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487204_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487204_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.783</v>
+        <v>5.9694</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8875</v>
+        <v>5.0471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8955</v>
+        <v>0.9223</v>
       </c>
       <c r="G2" t="n">
         <v>3.4386</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0416</v>
+        <v>0.1448</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0132</v>
+        <v>0.1729</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0549</v>
+        <v>-0.0281</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6617</v>
+        <v>5.2744</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5711</v>
+        <v>6.2909</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9094</v>
+        <v>-1.0165</v>
       </c>
       <c r="G3" t="n">
         <v>3.0948</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6491</v>
+        <v>-0.0364</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6266</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0225</v>
+        <v>-0.1296</v>
       </c>
       <c r="V3" t="n">
         <v>0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8457</v>
+        <v>0.7267</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7117</v>
+        <v>1.1067</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.866</v>
+        <v>-0.38</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5836</v>
+        <v>0.771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3726</v>
+        <v>0.8653</v>
       </c>
       <c r="I4" t="n">
-        <v>1.211</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0857</v>
+        <v>1.5985</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9236</v>
+        <v>1.9405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1621</v>
+        <v>-0.342</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5021</v>
+        <v>-0.8275</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.551</v>
+        <v>-1.0752</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0489</v>
+        <v>0.2478</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>0.3417</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7913</v>
+        <v>0.4733</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4713</v>
+        <v>-0.1316</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1213</v>
+        <v>0.5885</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4478</v>
+        <v>1.5883</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3265</v>
+        <v>-0.9999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.771</v>
+        <v>1.5836</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8653</v>
+        <v>0.3726</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09429999999999999</v>
+        <v>1.211</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5985</v>
+        <v>3.0857</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9405</v>
+        <v>2.9236</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.342</v>
+        <v>0.1621</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8275</v>
+        <v>-1.5021</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0752</v>
+        <v>-2.551</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2478</v>
+        <v>1.0489</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7363</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8144</v>
+        <v>0.668</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.078</v>
+        <v>-0.6052</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0634</v>
+        <v>0.0697</v>
       </c>
       <c r="E6" t="n">
-        <v>0.334</v>
+        <v>1.057</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3974</v>
+        <v>-0.9873</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3303</v>
+        <v>-0.4865</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9294</v>
+        <v>-2.6536</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4009</v>
+        <v>2.167</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3514</v>
+        <v>0.9625</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5924</v>
+        <v>-0.5434</v>
       </c>
       <c r="L6" t="n">
-        <v>2.759</v>
+        <v>1.5059</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0211</v>
+        <v>-1.449</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.663</v>
+        <v>-2.1102</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6419</v>
+        <v>0.6612</v>
       </c>
       <c r="P6" t="n">
-        <v>-6.1763</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.9133</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1263</v>
+        <v>-0.2158</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7681</v>
+        <v>0.0945</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3582</v>
+        <v>-0.3104</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1278</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3424</v>
+        <v>0.0512</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1784</v>
+        <v>0.0813</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.164</v>
+        <v>-0.0301</v>
       </c>
       <c r="G7" t="n">
         <v>0.1517</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4012</v>
+        <v>-0.0076</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2234</v>
+        <v>0.0364</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1778</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>D. RUIZ RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4846</v>
+        <v>-0.6849</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7972</v>
+        <v>-0.3415</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2818</v>
+        <v>-0.3434</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4865</v>
+        <v>-1.1449</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6536</v>
+        <v>-1.2606</v>
       </c>
       <c r="I8" t="n">
-        <v>2.167</v>
+        <v>0.1157</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9625</v>
+        <v>-0.5041</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5434</v>
+        <v>-0.6262</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5059</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.449</v>
+        <v>-0.6408</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1102</v>
+        <v>-0.6344</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6612</v>
+        <v>-0.0064</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.77</v>
+        <v>0.074</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>0.1626</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6048</v>
+        <v>-0.0886</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. RUIZ RUIZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1925</v>
+        <v>-0.9141</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7421</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4505</v>
+        <v>-0.8257</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1449</v>
+        <v>4.3303</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2606</v>
+        <v>0.9294</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1157</v>
+        <v>3.4009</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5041</v>
+        <v>5.3514</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6262</v>
+        <v>2.5924</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>2.759</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6408</v>
+        <v>-1.0211</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6344</v>
+        <v>-1.663</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0064</v>
+        <v>0.6419</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>-6.1763</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-7.9133</v>
       </c>
       <c r="R9" t="n">
-        <v>0.386</v>
+        <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4336</v>
+        <v>0.2756</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>0.3457</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1957</v>
+        <v>-0.0701</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4716</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4618</v>
+        <v>-1.0599</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8122</v>
+        <v>1.0408</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3504</v>
+        <v>-2.1006</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7614</v>
+        <v>-2.3473</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9863</v>
+        <v>-3.7404</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2249</v>
+        <v>1.3931</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3613</v>
+        <v>-1.2195</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6055</v>
+        <v>-2.5048</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2442</v>
+        <v>1.2853</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4001</v>
+        <v>-1.1278</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3808</v>
+        <v>-1.2356</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0193</v>
+        <v>0.1078</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.965</v>
+        <v>0.965</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1058</v>
+        <v>-0.9056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5208</v>
+        <v>-0.0026</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4151</v>
+        <v>-0.9029</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3704</v>
+        <v>1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3704</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9006</v>
+        <v>-1.1624</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5212</v>
+        <v>-2.3522</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4219</v>
+        <v>1.1898</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3473</v>
+        <v>-0.7614</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7404</v>
+        <v>-0.9863</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3931</v>
+        <v>0.2249</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2195</v>
+        <v>-0.3613</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.5048</v>
+        <v>-0.6055</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2853</v>
+        <v>0.2442</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1278</v>
+        <v>-0.4001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2356</v>
+        <v>-0.3808</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1078</v>
+        <v>-0.0193</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.965</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.158</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.7463</v>
+        <v>0.1937</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5221</v>
+        <v>-0.0608</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2242</v>
+        <v>0.2545</v>
       </c>
       <c r="V11" t="n">
-        <v>1.228</v>
+        <v>0.3704</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.228</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.966399999999999</v>
+        <v>8.858600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>12.5378</v>
+        <v>13.43</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5716</v>
+        <v>-4.5714</v>
       </c>
       <c r="G12" t="n">
         <v>8.629899999999999</v>
@@ -1378,7 +1378,7 @@
         <v>-13.5569</v>
       </c>
       <c r="O12" t="n">
-        <v>4.5126</v>
+        <v>4.512599999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-2.8952</v>
@@ -1390,13 +1390,13 @@
         <v>10.6154</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9649999999999997</v>
+        <v>-0.07279999999999995</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0909</v>
+        <v>1.9832</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0559</v>
+        <v>-2.056</v>
       </c>
       <c r="V12" t="n">
         <v>3.1967</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5584</v>
+        <v>1.8452</v>
       </c>
       <c r="E13" t="n">
-        <v>4.3153</v>
+        <v>1.5862</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.757</v>
+        <v>0.2589</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9738</v>
+        <v>0.9767</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3659</v>
+        <v>0.9781</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.392</v>
+        <v>-0.0014</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2748</v>
+        <v>1.4164</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2341</v>
+        <v>0.7245</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0407</v>
+        <v>0.6919</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3009</v>
+        <v>-0.4397</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8682</v>
+        <v>0.2536</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4327</v>
+        <v>-0.6933</v>
       </c>
       <c r="P13" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4687</v>
+        <v>0.0965</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0901</v>
+        <v>0.1699</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6214</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2702</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>D. PEREZ ABELLEIRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0185</v>
+        <v>1.5507</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8862</v>
+        <v>1.6304</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1323</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0407</v>
+        <v>0.9049</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8515</v>
+        <v>1.1291</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.8921</v>
+        <v>-0.2242</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7869</v>
+        <v>2.4718</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9186</v>
+        <v>1.1694</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1317</v>
+        <v>1.3024</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8275</v>
+        <v>-1.5669</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.0403</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7604</v>
+        <v>-1.5266</v>
       </c>
       <c r="P14" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R14" t="n">
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3524</v>
+        <v>-0.5123</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.1236</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8367</v>
+        <v>-0.6359</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7513</v>
+        <v>1.2899</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7865</v>
+        <v>2.9134</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0352</v>
+        <v>-1.6234</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9767</v>
+        <v>1.9738</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9781</v>
+        <v>2.3659</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0014</v>
+        <v>-0.392</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4164</v>
+        <v>3.2748</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7245</v>
+        <v>3.2341</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6919</v>
+        <v>0.0407</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4397</v>
+        <v>-1.3009</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2536</v>
+        <v>-0.8682</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6933</v>
+        <v>-0.4327</v>
       </c>
       <c r="P15" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0026</v>
+        <v>0.2003</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3702</v>
+        <v>0.6881</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3675</v>
+        <v>-0.4878</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.2702</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. PEREZ ABELLEIRA</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5228</v>
+        <v>1.1827</v>
       </c>
       <c r="E16" t="n">
-        <v>0.629</v>
+        <v>1.5858</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1061</v>
+        <v>-0.4031</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9049</v>
+        <v>-1.0407</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1291</v>
+        <v>2.8515</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2242</v>
+        <v>-3.8921</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4718</v>
+        <v>1.7869</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1694</v>
+        <v>2.9186</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3024</v>
+        <v>-1.1317</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5669</v>
+        <v>-2.8275</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0403</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5266</v>
+        <v>-2.7604</v>
       </c>
       <c r="P16" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5401</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8778</v>
+        <v>0.2152</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6623</v>
+        <v>0.3014</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1806</v>
+        <v>-0.1211</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5165</v>
+        <v>2.8169</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6971</v>
+        <v>-2.938</v>
       </c>
       <c r="G17" t="n">
         <v>1.6172</v>
@@ -1780,13 +1780,13 @@
         <v>2.5091</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1672</v>
+        <v>0.2267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1969</v>
+        <v>0.1035</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3641</v>
+        <v>0.1232</v>
       </c>
       <c r="V17" t="n">
         <v>-0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7089</v>
+        <v>-0.5622</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1223</v>
+        <v>0.078</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5866</v>
+        <v>-0.6402</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7776999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3173</v>
+        <v>-0.1705</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1785</v>
+        <v>0.0218</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1388</v>
+        <v>-0.1924</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8185</v>
+        <v>-0.8567</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4691</v>
+        <v>2.2702</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2876</v>
+        <v>-3.127</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1154</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3979</v>
+        <v>0.5638</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5949</v>
+        <v>0.2062</v>
       </c>
       <c r="U19" t="n">
-        <v>0.197</v>
+        <v>0.3576</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8842</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0607</v>
+        <v>-1.7923</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0868</v>
+        <v>-1.4874</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9738</v>
+        <v>-0.3049</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8028</v>
@@ -2014,13 +2014,13 @@
         <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3278</v>
+        <v>-0.0595</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4574</v>
+        <v>0.0569</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7853</v>
+        <v>-0.1164</v>
       </c>
       <c r="V20" t="n">
         <v>0.614</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2097</v>
+        <v>-4.7702</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5739</v>
+        <v>-4.375</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6358</v>
+        <v>-0.3952</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7889</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6491</v>
+        <v>0.0886</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2295</v>
+        <v>0.4283</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5804</v>
+        <v>-0.3398</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8391</v>
+        <v>-5.0647</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2481</v>
+        <v>-2.447</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5909</v>
+        <v>-2.6177</v>
       </c>
       <c r="G22" t="n">
         <v>-6.5771</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0919</v>
+        <v>0.6825</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7588</v>
+        <v>0.0423</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6669</v>
+        <v>0.6401</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3281</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.966499999999999</v>
+        <v>-7.2987</v>
       </c>
       <c r="E23" t="n">
         <v>4.571499999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.5378</v>
+        <v>-11.8703</v>
       </c>
       <c r="G23" t="n">
         <v>-8.629999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>13.5105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9649999999999997</v>
+        <v>1.6327</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0559</v>
+        <v>2.0558</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.091</v>
+        <v>-0.4233999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1967</v>
